--- a/02_DIA_inicio_2026_analisis_assets/rbd_9726_liceo-teniente-francisco-mery-aguirre_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9726_liceo-teniente-francisco-mery-aguirre_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{046ADB72-A6F5-40DD-88F0-A6699BD1861A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4740D890-01A5-42CE-B60F-09FDAE37D1DE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6A06D97-948A-474D-B1E3-8C06B9A41272}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E20A50D-D1A9-42E3-A93D-D0DF04DCBA09}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A7EA23-197B-440C-8AA5-75BD3105A6A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A71AD5-8FC9-43A4-BAC5-B630E41B1E14}"/>
 </file>